--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486893_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486893_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3087</v>
+        <v>5.5188</v>
       </c>
       <c r="E2" t="n">
-        <v>2.167</v>
+        <v>2.8218</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1417</v>
+        <v>2.697</v>
       </c>
       <c r="G2" t="n">
         <v>2.0811</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3001</v>
+        <v>-0.09</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9804</v>
+        <v>-0.3256</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6803</v>
+        <v>0.2356</v>
       </c>
       <c r="V2" t="n">
         <v>2.7063</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5463</v>
+        <v>2.9986</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0845</v>
+        <v>2.4181</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4619</v>
+        <v>0.5804</v>
       </c>
       <c r="G3" t="n">
         <v>2.7699</v>
@@ -688,13 +688,13 @@
         <v>0.616</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3657</v>
+        <v>-0.1821</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0731</v>
+        <v>0.4067</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7074</v>
+        <v>-0.5888</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2624</v>
+        <v>2.7589</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2176</v>
+        <v>1.3881</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0448</v>
+        <v>1.3708</v>
       </c>
       <c r="G4" t="n">
         <v>-0.008800000000000001</v>
@@ -766,13 +766,13 @@
         <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>0.38</v>
+        <v>0.8766</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.2555</v>
       </c>
       <c r="U4" t="n">
-        <v>0.295</v>
+        <v>0.6211</v>
       </c>
       <c r="V4" t="n">
         <v>1.0698</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1162</v>
+        <v>2.7174</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7907999999999999</v>
+        <v>1.0658</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3255</v>
+        <v>1.6515</v>
       </c>
       <c r="G5" t="n">
         <v>4.1584</v>
@@ -844,13 +844,13 @@
         <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.112</v>
+        <v>0.4892</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3566</v>
+        <v>-0.0815</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2446</v>
+        <v>0.5707</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6982</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7063</v>
+        <v>2.3405</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2473</v>
+        <v>-0.5538</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9536</v>
+        <v>2.8943</v>
       </c>
       <c r="G6" t="n">
         <v>0.5125</v>
@@ -922,13 +922,13 @@
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3339</v>
+        <v>0.3003</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1198</v>
+        <v>-0.4263</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7859</v>
+        <v>0.7266</v>
       </c>
       <c r="V6" t="n">
         <v>1.5277</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5807</v>
+        <v>0.5913</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0151</v>
+        <v>0.2643</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5958</v>
+        <v>0.327</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.9714</v>
+        <v>1.219</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.8059</v>
+        <v>0.1718</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1655</v>
+        <v>1.0472</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.2671</v>
+        <v>0.6634</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.7276</v>
+        <v>0.0584</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5395</v>
+        <v>0.605</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2957</v>
+        <v>0.5555</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.1134</v>
       </c>
       <c r="O7" t="n">
-        <v>0.374</v>
+        <v>0.4422</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2855</v>
+        <v>-0.4107</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1518</v>
+        <v>-0.6276</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6381</v>
+        <v>0.0116</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5137</v>
+        <v>-0.6392</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6591</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8993</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2636</v>
+        <v>0.1866</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0551</v>
+        <v>0.0698</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2085</v>
+        <v>0.1168</v>
       </c>
       <c r="G8" t="n">
-        <v>1.219</v>
+        <v>1.8283</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1718</v>
+        <v>0.2627</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0472</v>
+        <v>1.5656</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6634</v>
+        <v>1.3018</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0584</v>
+        <v>0.0389</v>
       </c>
       <c r="L8" t="n">
-        <v>0.605</v>
+        <v>1.2629</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5555</v>
+        <v>0.5264</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1134</v>
+        <v>0.2238</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4422</v>
+        <v>0.3027</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4107</v>
+        <v>-1.2321</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9554</v>
+        <v>-0.4097</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1976</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7578</v>
+        <v>-0.4097</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09760000000000001</v>
+        <v>-0.0974</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0698</v>
+        <v>0.1936</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0279</v>
+        <v>-0.291</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8283</v>
+        <v>-0.1341</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2627</v>
+        <v>-1.0024</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5656</v>
+        <v>0.8682</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3018</v>
+        <v>-0.1318</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0389</v>
+        <v>-0.6974</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2629</v>
+        <v>0.5656</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5264</v>
+        <v>-0.0023</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2238</v>
+        <v>-0.305</v>
       </c>
       <c r="O9" t="n">
         <v>0.3027</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4986</v>
+        <v>0.0717</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.3254</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4986</v>
+        <v>-0.2537</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
+          <t>A. DUVAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09130000000000001</v>
+        <v>-1.8113</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4415</v>
+        <v>-1.1101</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3502</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1341</v>
+        <v>-0.4254</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0024</v>
+        <v>-0.6909</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8682</v>
+        <v>0.2655</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1318</v>
+        <v>-0.4475</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6974</v>
+        <v>-0.2233</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5656</v>
+        <v>-0.2241</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0023</v>
+        <v>0.0221</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.305</v>
+        <v>-0.4676</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3027</v>
+        <v>0.4897</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2603</v>
+        <v>0.1685</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5733</v>
+        <v>0.3292</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.313</v>
+        <v>-0.1606</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2402</v>
+        <v>-0.9384</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1135</v>
+        <v>-1.9476</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1552</v>
+        <v>-3.832</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0417</v>
+        <v>1.8844</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.716</v>
+        <v>-2.9714</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9712</v>
+        <v>-2.8059</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2552</v>
+        <v>-0.1655</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1012</v>
+        <v>-3.2671</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8906</v>
+        <v>-2.7276</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7893</v>
+        <v>-0.5395</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6147</v>
+        <v>0.2957</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0807</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4659</v>
+        <v>0.374</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0267</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2321</v>
+        <v>-3.2855</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5204</v>
+        <v>1.6234</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1781</v>
+        <v>0.8212</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3423</v>
+        <v>0.8022</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1088</v>
+        <v>1.6591</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.8993</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1088</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. DUVAL</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2642</v>
+        <v>-2.0072</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3852</v>
+        <v>-1.8414</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.879</v>
+        <v>-0.1658</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4254</v>
+        <v>-1.716</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6909</v>
+        <v>-2.9712</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2655</v>
+        <v>1.2552</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4475</v>
+        <v>-1.1012</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2233</v>
+        <v>-1.8906</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2241</v>
+        <v>0.7893</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0221</v>
+        <v>-0.6147</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4676</v>
+        <v>-1.0807</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4897</v>
+        <v>0.4659</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.616</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R12" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2844</v>
+        <v>0.6267</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0541</v>
+        <v>0.4919</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3385</v>
+        <v>0.1348</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9384</v>
+        <v>0.1088</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1786</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.131</v>
+        <v>-4.1254</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9952</v>
+        <v>-3.1971</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1358</v>
+        <v>-0.9283</v>
       </c>
       <c r="G13" t="n">
         <v>-1.0106</v>
@@ -1468,13 +1468,13 @@
         <v>1.2321</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8884</v>
+        <v>0.1172</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3798</v>
+        <v>0.4183</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.3011</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1786</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.464400000000001</v>
+        <v>7.123200000000003</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.971699999999999</v>
+        <v>-2.3129</v>
       </c>
       <c r="F14" t="n">
-        <v>9.436400000000003</v>
+        <v>9.435999999999998</v>
       </c>
       <c r="G14" t="n">
-        <v>6.3029</v>
+        <v>6.302900000000002</v>
       </c>
       <c r="H14" t="n">
         <v>-2.6438</v>
@@ -1525,7 +1525,7 @@
         <v>0.2308000000000006</v>
       </c>
       <c r="L14" t="n">
-        <v>4.6288</v>
+        <v>4.628800000000001</v>
       </c>
       <c r="M14" t="n">
         <v>1.4433</v>
@@ -1546,13 +1546,13 @@
         <v>11.2937</v>
       </c>
       <c r="S14" t="n">
-        <v>2.305400000000001</v>
+        <v>2.9642</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5675</v>
+        <v>2.2264</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7378999999999999</v>
+        <v>0.7379000000000002</v>
       </c>
       <c r="V14" t="n">
         <v>4.016299999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1081</v>
+        <v>4.2155</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4223</v>
+        <v>2.2716</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6859</v>
+        <v>1.9439</v>
       </c>
       <c r="G15" t="n">
         <v>2.457</v>
@@ -1624,13 +1624,13 @@
         <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1521</v>
+        <v>0.2595</v>
       </c>
       <c r="T15" t="n">
-        <v>1.348</v>
+        <v>0.1973</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1958</v>
+        <v>0.0622</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3491</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5957</v>
+        <v>2.1663</v>
       </c>
       <c r="E16" t="n">
-        <v>1.053</v>
+        <v>0.5043</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5427</v>
+        <v>1.662</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3746</v>
+        <v>-0.0235</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2849</v>
+        <v>0.2007</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0897</v>
+        <v>-0.2241</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4368</v>
+        <v>-0.2402</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2789</v>
+        <v>0.1947</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1579</v>
+        <v>-0.4349</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0622</v>
+        <v>0.2167</v>
       </c>
       <c r="N16" t="n">
         <v>0.006</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0682</v>
+        <v>0.2107</v>
       </c>
       <c r="P16" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6694</v>
+        <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6132</v>
+        <v>-0.3565</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6696</v>
+        <v>-0.4342</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0564</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.0082</v>
+        <v>0.6982</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.0082</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7297</v>
+        <v>0.3954</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4372</v>
+        <v>0.0708</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1668</v>
+        <v>0.3246</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0235</v>
+        <v>0.0545</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2007</v>
+        <v>0.5254</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2241</v>
+        <v>-0.4709</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2402</v>
+        <v>0.1173</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1947</v>
+        <v>0.0779</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4349</v>
+        <v>0.0395</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2167</v>
+        <v>-0.0629</v>
       </c>
       <c r="N17" t="n">
-        <v>0.006</v>
+        <v>0.4475</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2107</v>
+        <v>-0.5104</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8481</v>
+        <v>0.4107</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>0.4107</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7931</v>
+        <v>-0.0697</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3756</v>
+        <v>-0.0466</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4175</v>
+        <v>-0.0232</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1862</v>
+        <v>0.2502</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1384</v>
+        <v>-0.8857</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3246</v>
+        <v>1.1359</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0545</v>
+        <v>-1.262</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5254</v>
+        <v>-0.8302</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4709</v>
+        <v>-0.4318</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1173</v>
+        <v>0.2601</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0779</v>
+        <v>-0.0024</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0395</v>
+        <v>0.2625</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0629</v>
+        <v>-1.5221</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4475</v>
+        <v>-0.8278</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5104</v>
+        <v>-0.6943</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4107</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4107</v>
+        <v>2.6694</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2789</v>
+        <v>-0.3255</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2558</v>
+        <v>-0.3141</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0232</v>
+        <v>-0.0114</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.2484</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.2484</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1612</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5133</v>
+        <v>-0.4115</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3522</v>
+        <v>0.5043</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.262</v>
+        <v>1.3746</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8302</v>
+        <v>1.2849</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4318</v>
+        <v>0.0897</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2601</v>
+        <v>1.4368</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0024</v>
+        <v>1.2789</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2625</v>
+        <v>0.1579</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5221</v>
+        <v>-0.0622</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8278</v>
+        <v>0.006</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6943</v>
+        <v>-0.0682</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R19" t="n">
         <v>2.6694</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7369</v>
+        <v>0.1104</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9417</v>
+        <v>0.2051</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2048</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>2.2484</v>
+        <v>-2.0082</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2484</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2782</v>
+        <v>-1.4223</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8752</v>
+        <v>-0.9799</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4029</v>
+        <v>-0.4424</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3269</v>
@@ -2014,13 +2014,13 @@
         <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4327</v>
+        <v>0.2886</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4416</v>
+        <v>0.337</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0089</v>
+        <v>-0.0484</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5589</v>
+        <v>-1.4351</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8524</v>
+        <v>0.7478</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4113</v>
+        <v>-2.1829</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1981</v>
@@ -2092,13 +2092,13 @@
         <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3537</v>
+        <v>0.4775</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3408</v>
+        <v>0.2361</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0129</v>
+        <v>0.2413</v>
       </c>
       <c r="V21" t="n">
         <v>-2.9466</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7944</v>
+        <v>-1.6713</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4764</v>
+        <v>-0.642</v>
       </c>
       <c r="F22" t="n">
-        <v>1.682</v>
+        <v>-1.0294</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7298</v>
+        <v>-2.0258</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6879</v>
+        <v>0.0712</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0419</v>
+        <v>-2.097</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5542</v>
+        <v>-0.5606</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5806</v>
+        <v>0.0973</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9737</v>
+        <v>-0.6579</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1756</v>
+        <v>-1.4653</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1074</v>
+        <v>-0.0261</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0682</v>
+        <v>-1.4392</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5247000000000001</v>
+        <v>-0.2616</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1045</v>
+        <v>-0.0814</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4202</v>
+        <v>-0.1801</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1839</v>
+        <v>-1.761</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9558</v>
+        <v>-3.2405</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2281</v>
+        <v>1.4795</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0258</v>
+        <v>-1.727</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0712</v>
+        <v>-0.4638</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.097</v>
+        <v>-1.2633</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5606</v>
+        <v>-1.0939</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0973</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6579</v>
+        <v>-0.29</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4653</v>
+        <v>-0.6331</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0261</v>
+        <v>0.3401</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4392</v>
+        <v>-0.9732</v>
       </c>
       <c r="P23" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R23" t="n">
-        <v>0.616</v>
+        <v>2.4641</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7741</v>
+        <v>-0.4446</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3952</v>
+        <v>-0.3334</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3789</v>
+        <v>-0.1112</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6449</v>
+        <v>-1.9898</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6589</v>
+        <v>-3.4764</v>
       </c>
       <c r="F24" t="n">
-        <v>1.014</v>
+        <v>1.4867</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.727</v>
+        <v>-2.7298</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4638</v>
+        <v>-0.6879</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2633</v>
+        <v>-2.0419</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0939</v>
+        <v>-2.5542</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.5806</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.29</v>
+        <v>-1.9737</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6331</v>
+        <v>-0.1756</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3401</v>
+        <v>-0.1074</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9732</v>
+        <v>-0.0682</v>
       </c>
       <c r="P24" t="n">
         <v>0.4107</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4641</v>
+        <v>1.4374</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3286</v>
+        <v>0.3294</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7518</v>
+        <v>0.1045</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5768</v>
+        <v>0.2249</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4626</v>
+        <v>-3.7566</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7084</v>
+        <v>-3.29</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7542</v>
+        <v>-0.4665</v>
       </c>
       <c r="G25" t="n">
         <v>0.1042</v>
@@ -2404,13 +2404,13 @@
         <v>1.6427</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4703</v>
+        <v>-0.7642</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9222</v>
+        <v>-0.5038</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5481</v>
+        <v>-0.2604</v>
       </c>
       <c r="V25" t="n">
         <v>-1.6591</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.464399999999999</v>
+        <v>-4.915900000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.4359</v>
+        <v>-9.3315</v>
       </c>
       <c r="F26" t="n">
-        <v>2.9717</v>
+        <v>4.4157</v>
       </c>
       <c r="G26" t="n">
         <v>-6.3028</v>
@@ -2467,13 +2467,13 @@
         <v>-4.859699999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2309</v>
+        <v>-0.2308999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>-4.628699999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>6.160299999999999</v>
+        <v>6.1603</v>
       </c>
       <c r="Q26" t="n">
         <v>-11.2937</v>
@@ -2482,16 +2482,16 @@
         <v>17.454</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.3055</v>
+        <v>-0.7566999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7378000000000001</v>
+        <v>-0.6335</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.5677</v>
+        <v>-0.1233</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.0164</v>
+        <v>-4.016400000000001</v>
       </c>
       <c r="W26" t="n">
         <v>4.0388</v>
